--- a/JsonConverter/ExcelFiles/PetPassiveSkillData.xlsx
+++ b/JsonConverter/ExcelFiles/PetPassiveSkillData.xlsx
@@ -493,6 +493,9 @@
       <c r="G4" s="4" t="s">
         <v>23</v>
       </c>
+      <c r="H4" s="4">
+        <v>5.0</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="s">
@@ -512,6 +515,9 @@
       </c>
       <c r="G5" s="4" t="s">
         <v>23</v>
+      </c>
+      <c r="H5" s="4">
+        <v>5.0</v>
       </c>
     </row>
   </sheetData>

--- a/JsonConverter/ExcelFiles/PetPassiveSkillData.xlsx
+++ b/JsonConverter/ExcelFiles/PetPassiveSkillData.xlsx
@@ -435,8 +435,8 @@
       <c r="D2" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="E2" s="1" t="s">
-        <v>9</v>
+      <c r="E2" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="F2" s="3" t="s">
         <v>9</v>
